--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N206_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N206_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.13447121062099</v>
+        <v>2.946851571725911</v>
       </c>
       <c r="D2" t="n">
-        <v>17.74013810543762</v>
+        <v>2.882772442133613</v>
       </c>
       <c r="E2" t="n">
-        <v>10.82136444066747</v>
+        <v>1.758471721608464</v>
       </c>
       <c r="F2" t="n">
-        <v>11.28174043083878</v>
+        <v>1.833282820011301</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.85518121561432</v>
+        <v>1.763966947537328</v>
       </c>
       <c r="D3" t="n">
-        <v>10.84010297727629</v>
+        <v>1.761516733807397</v>
       </c>
       <c r="E3" t="n">
-        <v>10.82136444066747</v>
+        <v>1.758471721608464</v>
       </c>
       <c r="F3" t="n">
-        <v>11.28174043083878</v>
+        <v>1.833282820011301</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.72179711028711</v>
+        <v>3.692292030421655</v>
       </c>
       <c r="D4" t="n">
-        <v>10.51189802081432</v>
+        <v>1.708183428382327</v>
       </c>
       <c r="E4" t="n">
-        <v>10.82136444066747</v>
+        <v>1.758471721608464</v>
       </c>
       <c r="F4" t="n">
-        <v>11.28174043083878</v>
+        <v>1.833282820011301</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.54234832640691</v>
+        <v>3.988131603041123</v>
       </c>
       <c r="D5" t="n">
-        <v>21.02042640387905</v>
+        <v>3.415819290630345</v>
       </c>
       <c r="E5" t="n">
-        <v>10.82136444066747</v>
+        <v>1.758471721608464</v>
       </c>
       <c r="F5" t="n">
-        <v>11.28174043083878</v>
+        <v>1.833282820011301</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.94339623842965</v>
+        <v>6.978301888744818</v>
       </c>
       <c r="D6" t="n">
-        <v>39.52354260189427</v>
+        <v>6.422575672807819</v>
       </c>
       <c r="E6" t="n">
-        <v>10.82136444066747</v>
+        <v>1.758471721608464</v>
       </c>
       <c r="F6" t="n">
-        <v>11.28174043083878</v>
+        <v>1.833282820011301</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.71317530561289</v>
+        <v>6.290890987162095</v>
       </c>
       <c r="D7" t="n">
-        <v>38.55938197464931</v>
+        <v>6.265899570880514</v>
       </c>
       <c r="E7" t="n">
-        <v>10.82136444066747</v>
+        <v>1.758471721608464</v>
       </c>
       <c r="F7" t="n">
-        <v>11.28174043083878</v>
+        <v>1.833282820011301</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.19348779664458</v>
+        <v>5.718941766954745</v>
       </c>
       <c r="D8" t="n">
-        <v>29.90029558081354</v>
+        <v>4.858798031882201</v>
       </c>
       <c r="E8" t="n">
-        <v>10.82136444066747</v>
+        <v>1.758471721608464</v>
       </c>
       <c r="F8" t="n">
-        <v>11.28174043083878</v>
+        <v>1.833282820011301</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
